--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.6380,0.0360,0.1264,0.1914</t>
-  </si>
-  <si>
-    <t>0.0132,0.0045,0.0018,0.9930</t>
-  </si>
-  <si>
-    <t>0.9139,0.0106,0.0074,0.0521</t>
-  </si>
-  <si>
-    <t>0.0046,0.0044,0.0016,0.9963</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9938,0.0034,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9817,0.0122,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9841,0.0086,0.0032,0.0011</t>
-  </si>
-  <si>
-    <t>0.9769,0.0363,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9934,0.0054,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9959,0.0017,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9933,0.0019,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.7674,0.0585,0.1530,0.0110</t>
-  </si>
-  <si>
-    <t>0.2187,0.0491,0.8338,0.0032</t>
-  </si>
-  <si>
-    <t>0.2020,0.1048,0.7540,0.0014</t>
-  </si>
-  <si>
-    <t>0.1111,0.0342,0.8852,0.0046</t>
-  </si>
-  <si>
-    <t>0.7970,0.0671,0.1120,0.0249</t>
-  </si>
-  <si>
-    <t>0.0074,0.9868,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.0346,0.9772,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.4912,0.6153,0.0080,0.0041</t>
-  </si>
-  <si>
-    <t>0.0066,0.9900,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9921,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.5347,0.0173,0.3882,0.0555</t>
-  </si>
-  <si>
-    <t>0.5472,0.0528,0.5046,0.0126</t>
-  </si>
-  <si>
-    <t>0.0280,0.0139,0.9746,0.0009</t>
-  </si>
-  <si>
-    <t>0.1209,0.0110,0.9007,0.0045</t>
-  </si>
-  <si>
-    <t>0.0073,0.0034,0.9804,0.0096</t>
-  </si>
-  <si>
-    <t>0.0518,0.0053,0.9521,0.0066</t>
-  </si>
-  <si>
-    <t>0.0092,0.0083,0.9570,0.0401</t>
-  </si>
-  <si>
-    <t>0.5954,0.5158,0.0159,0.0032</t>
-  </si>
-  <si>
-    <t>0.7041,0.1753,0.1652,0.0117</t>
-  </si>
-  <si>
-    <t>0.0040,0.0341,0.9729,0.0119</t>
-  </si>
-  <si>
-    <t>0.0102,0.9274,0.1277,0.0006</t>
-  </si>
-  <si>
-    <t>0.7269,0.2565,0.0588,0.0301</t>
-  </si>
-  <si>
-    <t>0.7993,0.2104,0.0357,0.0036</t>
-  </si>
-  <si>
-    <t>0.6886,0.4826,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.0324,0.9164,0.2683,0.0079</t>
-  </si>
-  <si>
-    <t>0.0163,0.7802,0.4958,0.0183</t>
-  </si>
-  <si>
-    <t>0.1534,0.2248,0.7637,0.0806</t>
-  </si>
-  <si>
-    <t>0.0313,0.3723,0.9153,0.0053</t>
-  </si>
-  <si>
-    <t>0.0359,0.0083,0.8417,0.2785</t>
-  </si>
-  <si>
-    <t>0.0396,0.0957,0.9306,0.0008</t>
-  </si>
-  <si>
-    <t>0.0030,0.9816,0.0067,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.1779,0.9834,0.0012</t>
-  </si>
-  <si>
-    <t>0.0717,0.6542,0.0166,0.6533</t>
-  </si>
-  <si>
-    <t>0.0069,0.9838,0.0024,0.0026</t>
-  </si>
-  <si>
-    <t>0.0023,0.9853,0.0360,0.0018</t>
-  </si>
-  <si>
-    <t>0.0044,0.9815,0.0440,0.0018</t>
-  </si>
-  <si>
-    <t>0.0024,0.1092,0.9308,0.0408</t>
-  </si>
-  <si>
-    <t>0.0081,0.1238,0.9618,0.0027</t>
-  </si>
-  <si>
-    <t>0.0264,0.0262,0.9299,0.0151</t>
-  </si>
-  <si>
-    <t>0.0949,0.0067,0.9341,0.0044</t>
-  </si>
-  <si>
-    <t>0.0059,0.0095,0.9850,0.0051</t>
-  </si>
-  <si>
-    <t>0.0488,0.0464,0.9573,0.0007</t>
-  </si>
-  <si>
-    <t>0.8204,0.2786,0.0031,0.0034</t>
-  </si>
-  <si>
-    <t>0.9820,0.0062,0.0011,0.0038</t>
-  </si>
-  <si>
-    <t>0.7689,0.2940,0.0136,0.0063</t>
-  </si>
-  <si>
-    <t>0.0147,0.0248,0.9550,0.0286</t>
-  </si>
-  <si>
-    <t>0.9506,0.0354,0.0035,0.0076</t>
-  </si>
-  <si>
-    <t>0.9864,0.0147,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9736,0.0232,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.0054,0.7847,0.8985,0.0009</t>
-  </si>
-  <si>
-    <t>0.0038,0.0495,0.9824,0.0036</t>
-  </si>
-  <si>
-    <t>0.0006,0.0044,0.9779,0.0748</t>
-  </si>
-  <si>
-    <t>0.0003,0.9793,0.6213,0.0012</t>
-  </si>
-  <si>
-    <t>0.0060,0.0174,0.9738,0.0082</t>
-  </si>
-  <si>
-    <t>0.0057,0.9791,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.0076,0.9826,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.8782,0.0363,0.1043,0.0071</t>
-  </si>
-  <si>
-    <t>0.7005,0.1186,0.2718,0.0153</t>
-  </si>
-  <si>
-    <t>0.0026,0.0344,0.9837,0.0031</t>
-  </si>
-  <si>
-    <t>0.0005,0.8979,0.9628,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9024,0.9275,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9789,0.7216,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.8937,0.9164,0.0002</t>
-  </si>
-  <si>
-    <t>0.0444,0.0135,0.0071,0.9722</t>
-  </si>
-  <si>
-    <t>0.0005,0.0462,0.0001,0.9983</t>
-  </si>
-  <si>
-    <t>0.0023,0.0015,0.0003,0.9987</t>
-  </si>
-  <si>
-    <t>0.0286,0.0083,0.0030,0.9847</t>
-  </si>
-  <si>
-    <t>0.0630,0.0055,0.0100,0.9653</t>
-  </si>
-  <si>
-    <t>0.0052,0.0046,0.0008,0.9969</t>
-  </si>
-  <si>
-    <t>0.0001,0.9804,0.8467,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.8902,0.9527,0.0001</t>
-  </si>
-  <si>
-    <t>0.0174,0.5372,0.8741,0.0042</t>
-  </si>
-  <si>
-    <t>0.0088,0.6105,0.9234,0.0038</t>
-  </si>
-  <si>
-    <t>0.0002,0.9601,0.9569,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9606,0.2929,0.0003</t>
-  </si>
-  <si>
-    <t>0.9874,0.0158,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9384,0.1075,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.9146,0.1703,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9677,0.0320,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.9829,0.0208,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9863,0.0112,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9669,0.0606,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9835,0.0215,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9941,0.0018,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9937,0.0064,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0013,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9974,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9950,0.0003,0.0000,0.0031</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0366,0.0093,0.9663,0.0033</t>
-  </si>
-  <si>
-    <t>0.5265,0.0288,0.4682,0.0265</t>
-  </si>
-  <si>
-    <t>0.7459,0.0136,0.1921,0.0330</t>
-  </si>
-  <si>
-    <t>0.0078,0.0143,0.9873,0.0007</t>
-  </si>
-  <si>
-    <t>0.0216,0.9713,0.0042,0.0008</t>
-  </si>
-  <si>
-    <t>0.0277,0.9716,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.0500,0.9634,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.1192,0.9194,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.0303,0.9652,0.0083,0.0011</t>
-  </si>
-  <si>
-    <t>0.0091,0.9851,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.1380,0.9002,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.8030,0.0627,0.0971,0.0208</t>
-  </si>
-  <si>
-    <t>0.4091,0.0184,0.5851,0.0427</t>
-  </si>
-  <si>
-    <t>0.3488,0.5915,0.0646,0.0304</t>
-  </si>
-  <si>
-    <t>0.5575,0.1956,0.2525,0.0427</t>
-  </si>
-  <si>
-    <t>0.0496,0.1687,0.0461,0.9258</t>
-  </si>
-  <si>
-    <t>0.0037,0.9911,0.0106,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9927,0.0032,0.0123</t>
-  </si>
-  <si>
-    <t>0.0191,0.8119,0.0465,0.2611</t>
-  </si>
-  <si>
-    <t>0.0010,0.8684,0.9488,0.0004</t>
-  </si>
-  <si>
-    <t>0.0119,0.9811,0.0626,0.0001</t>
-  </si>
-  <si>
-    <t>0.2710,0.7358,0.0574,0.0020</t>
-  </si>
-  <si>
-    <t>0.2557,0.7714,0.0361,0.0005</t>
-  </si>
-  <si>
-    <t>0.9549,0.0300,0.0059,0.0046</t>
-  </si>
-  <si>
-    <t>0.9722,0.0155,0.0051,0.0034</t>
-  </si>
-  <si>
-    <t>0.9864,0.0030,0.0016,0.0038</t>
-  </si>
-  <si>
-    <t>0.9898,0.0021,0.0013,0.0016</t>
-  </si>
-  <si>
-    <t>0.9880,0.0104,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9756,0.0041,0.0082,0.0044</t>
-  </si>
-  <si>
-    <t>0.9928,0.0012,0.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.9934,0.0005,0.0001,0.0031</t>
-  </si>
-  <si>
-    <t>0.0016,0.9022,0.9399,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.8888,0.9756,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.4058,0.9633,0.0007</t>
-  </si>
-  <si>
-    <t>0.0191,0.3509,0.8887,0.0010</t>
-  </si>
-  <si>
-    <t>0.7757,0.1455,0.0518,0.0081</t>
-  </si>
-  <si>
-    <t>0.6141,0.1258,0.2649,0.0553</t>
-  </si>
-  <si>
-    <t>0.4183,0.0173,0.5674,0.0554</t>
-  </si>
-  <si>
-    <t>0.6364,0.0911,0.3188,0.0169</t>
-  </si>
-  <si>
-    <t>0.1098,0.0034,0.0062,0.9481</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.0003,0.9995</t>
-  </si>
-  <si>
-    <t>0.0006,0.0058,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0079,0.0007,0.0012,0.9961</t>
-  </si>
-  <si>
-    <t>0.0016,0.9297,0.5691,0.0015</t>
-  </si>
-  <si>
-    <t>0.9763,0.0253,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.1813,0.8232,0.0037,0.0128</t>
-  </si>
-  <si>
-    <t>0.9878,0.0028,0.0012,0.0028</t>
-  </si>
-  <si>
-    <t>0.6730,0.3570,0.0416,0.0150</t>
-  </si>
-  <si>
-    <t>0.9786,0.0064,0.0090,0.0016</t>
-  </si>
-  <si>
-    <t>0.2697,0.0033,0.0026,0.8870</t>
-  </si>
-  <si>
-    <t>0.9653,0.0076,0.0132,0.0052</t>
-  </si>
-  <si>
-    <t>0.0004,0.0194,0.9892,0.0112</t>
-  </si>
-  <si>
-    <t>0.8969,0.0003,0.0033,0.0880</t>
-  </si>
-  <si>
-    <t>0.8807,0.0062,0.0136,0.0792</t>
-  </si>
-  <si>
-    <t>0.3278,0.7026,0.0320,0.0349</t>
-  </si>
-  <si>
-    <t>0.8862,0.1086,0.0067,0.0067</t>
-  </si>
-  <si>
-    <t>0.9202,0.0529,0.0147,0.0058</t>
-  </si>
-  <si>
-    <t>0.2121,0.7650,0.1239,0.0628</t>
-  </si>
-  <si>
-    <t>0.7796,0.1521,0.0547,0.0201</t>
-  </si>
-  <si>
-    <t>0.8551,0.1589,0.0105,0.0048</t>
-  </si>
-  <si>
-    <t>0.9932,0.0018,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9857,0.0073,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9945,0.0025,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0023,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9872,0.0065,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9881,0.0094,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9872,0.0080,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9924,0.0016,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.5517,0.4891,0.0048,0.0126</t>
-  </si>
-  <si>
-    <t>0.1382,0.9103,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.6058,0.5482,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.0485,0.1555,0.9433,0.0016</t>
-  </si>
-  <si>
-    <t>0.9850,0.0154,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9525,0.0279,0.0066,0.0067</t>
-  </si>
-  <si>
-    <t>0.8370,0.3106,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9478,0.0617,0.0072,0.0009</t>
-  </si>
-  <si>
-    <t>0.0021,0.0907,0.9887,0.0004</t>
-  </si>
-  <si>
-    <t>0.9502,0.0459,0.0111,0.0019</t>
-  </si>
-  <si>
-    <t>0.0044,0.0125,0.9902,0.0008</t>
-  </si>
-  <si>
-    <t>0.0040,0.4857,0.9496,0.0024</t>
-  </si>
-  <si>
-    <t>0.0066,0.0198,0.9821,0.0025</t>
-  </si>
-  <si>
-    <t>0.0104,0.3299,0.9429,0.0037</t>
-  </si>
-  <si>
-    <t>0.0373,0.0107,0.9623,0.0019</t>
-  </si>
-  <si>
-    <t>0.0093,0.0027,0.9877,0.0005</t>
-  </si>
-  <si>
-    <t>0.0310,0.0115,0.9669,0.0008</t>
-  </si>
-  <si>
-    <t>0.5386,0.1577,0.4157,0.0193</t>
-  </si>
-  <si>
-    <t>0.5900,0.0094,0.6238,0.0011</t>
-  </si>
-  <si>
-    <t>0.6512,0.2122,0.1706,0.0088</t>
-  </si>
-  <si>
-    <t>0.4335,0.1517,0.4946,0.0074</t>
-  </si>
-  <si>
-    <t>0.3769,0.4880,0.2105,0.0055</t>
-  </si>
-  <si>
-    <t>0.6851,0.0856,0.2272,0.0064</t>
-  </si>
-  <si>
-    <t>0.2851,0.3016,0.4692,0.0505</t>
-  </si>
-  <si>
-    <t>0.1285,0.2143,0.7419,0.0039</t>
-  </si>
-  <si>
-    <t>0.8450,0.2323,0.0113,0.0007</t>
-  </si>
-  <si>
-    <t>0.1696,0.8715,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.8814,0.2201,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9534,0.0919,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.7227,0.3841,0.0103,0.0009</t>
-  </si>
-  <si>
-    <t>0.4953,0.3552,0.2518,0.0456</t>
-  </si>
-  <si>
-    <t>0.8378,0.0168,0.1548,0.0043</t>
-  </si>
-  <si>
-    <t>0.2669,0.0772,0.0473,0.7245</t>
-  </si>
-  <si>
-    <t>0.4556,0.1541,0.4839,0.0417</t>
-  </si>
-  <si>
-    <t>0.6550,0.0383,0.3650,0.0022</t>
-  </si>
-  <si>
-    <t>0.0155,0.0258,0.9462,0.0423</t>
-  </si>
-  <si>
-    <t>0.0154,0.4160,0.8969,0.0008</t>
-  </si>
-  <si>
-    <t>0.0185,0.2688,0.9230,0.0055</t>
-  </si>
-  <si>
-    <t>0.0415,0.0646,0.9534,0.0024</t>
-  </si>
-  <si>
-    <t>0.0252,0.4556,0.7323,0.0141</t>
-  </si>
-  <si>
-    <t>0.9861,0.0088,0.0012,0.0012</t>
-  </si>
-  <si>
-    <t>0.9746,0.0297,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9790,0.0149,0.0010,0.0027</t>
-  </si>
-  <si>
-    <t>0.9658,0.0500,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.9499,0.0594,0.0095,0.0014</t>
-  </si>
-  <si>
-    <t>0.9880,0.0098,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9940,0.0016,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.0580,0.1697,0.8319,0.0685</t>
-  </si>
-  <si>
-    <t>0.2586,0.4467,0.4226,0.0101</t>
-  </si>
-  <si>
-    <t>0.8451,0.0225,0.0935,0.0273</t>
-  </si>
-  <si>
-    <t>0.0240,0.0134,0.9686,0.0065</t>
-  </si>
-  <si>
-    <t>0.0081,0.0263,0.9811,0.0017</t>
-  </si>
-  <si>
-    <t>0.0301,0.2331,0.8638,0.0022</t>
-  </si>
-  <si>
-    <t>0.0005,0.0194,0.9960,0.0008</t>
-  </si>
-  <si>
-    <t>0.0836,0.0989,0.8467,0.0029</t>
-  </si>
-  <si>
-    <t>0.0026,0.0132,0.9952,0.0003</t>
-  </si>
-  <si>
-    <t>0.0157,0.0448,0.9580,0.0066</t>
-  </si>
-  <si>
-    <t>0.0347,0.1072,0.9306,0.0036</t>
-  </si>
-  <si>
-    <t>0.6705,0.0110,0.2523,0.0531</t>
-  </si>
-  <si>
-    <t>0.4144,0.0772,0.6243,0.0134</t>
-  </si>
-  <si>
-    <t>0.8849,0.0097,0.0473,0.0200</t>
-  </si>
-  <si>
-    <t>0.9788,0.0145,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9896,0.0151,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0109,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9814,0.0162,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.9621,0.0548,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9728,0.0535,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.8840,0.1838,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.9857,0.0086,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.0153,0.6699,0.5663,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.4132,0.9420,0.0007</t>
-  </si>
-  <si>
-    <t>0.0022,0.2134,0.9885,0.0002</t>
-  </si>
-  <si>
-    <t>0.0902,0.2212,0.6791,0.0046</t>
-  </si>
-  <si>
-    <t>0.0012,0.0027,0.9935,0.0040</t>
-  </si>
-  <si>
-    <t>0.2379,0.0472,0.7164,0.0346</t>
-  </si>
-  <si>
-    <t>0.1519,0.0385,0.8335,0.0033</t>
-  </si>
-  <si>
-    <t>0.0043,0.1003,0.5199,0.5689</t>
-  </si>
-  <si>
-    <t>0.7709,0.0193,0.1343,0.0759</t>
-  </si>
-  <si>
-    <t>0.1116,0.0154,0.0068,0.9489</t>
-  </si>
-  <si>
-    <t>0.0038,0.0154,0.0009,0.9958</t>
-  </si>
-  <si>
-    <t>0.0059,0.0025,0.0055,0.9944</t>
-  </si>
-  <si>
-    <t>0.0009,0.0024,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.3740,0.1105,0.0292,0.6444</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6467,0.1897,0.0088,0.1163</t>
+  </si>
+  <si>
+    <t>0.0052,0.0116,0.0013,0.9957</t>
+  </si>
+  <si>
+    <t>0.6151,0.0217,0.0012,0.3490</t>
+  </si>
+  <si>
+    <t>0.0166,0.0100,0.0030,0.9892</t>
+  </si>
+  <si>
+    <t>0.9921,0.0072,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0014,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9852,0.0154,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9810,0.0198,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9727,0.0378,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0018,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0022,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.6122,0.2127,0.0343,0.0870</t>
+  </si>
+  <si>
+    <t>0.4523,0.0473,0.5806,0.0242</t>
+  </si>
+  <si>
+    <t>0.4805,0.0174,0.6811,0.0025</t>
+  </si>
+  <si>
+    <t>0.0432,0.0559,0.9305,0.0031</t>
+  </si>
+  <si>
+    <t>0.4843,0.1117,0.4560,0.1224</t>
+  </si>
+  <si>
+    <t>0.0010,0.9969,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.9879,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.1850,0.8748,0.0069,0.0025</t>
+  </si>
+  <si>
+    <t>0.0343,0.9651,0.0094,0.0005</t>
+  </si>
+  <si>
+    <t>0.0046,0.9910,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.6877,0.0130,0.2829,0.0334</t>
+  </si>
+  <si>
+    <t>0.3554,0.1020,0.5556,0.0703</t>
+  </si>
+  <si>
+    <t>0.0683,0.0662,0.9060,0.0019</t>
+  </si>
+  <si>
+    <t>0.0913,0.0227,0.8664,0.0282</t>
+  </si>
+  <si>
+    <t>0.0380,0.0089,0.9542,0.0074</t>
+  </si>
+  <si>
+    <t>0.1575,0.0155,0.8580,0.0044</t>
+  </si>
+  <si>
+    <t>0.0160,0.0048,0.9705,0.0063</t>
+  </si>
+  <si>
+    <t>0.5983,0.4685,0.0186,0.0177</t>
+  </si>
+  <si>
+    <t>0.1714,0.3203,0.6597,0.0036</t>
+  </si>
+  <si>
+    <t>0.0045,0.0069,0.9925,0.0017</t>
+  </si>
+  <si>
+    <t>0.0172,0.8886,0.1874,0.0018</t>
+  </si>
+  <si>
+    <t>0.8030,0.1849,0.0101,0.0131</t>
+  </si>
+  <si>
+    <t>0.8466,0.1137,0.0532,0.0076</t>
+  </si>
+  <si>
+    <t>0.7050,0.4810,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.0272,0.9447,0.0647,0.0074</t>
+  </si>
+  <si>
+    <t>0.0011,0.9555,0.0128,0.0252</t>
+  </si>
+  <si>
+    <t>0.1423,0.0805,0.8439,0.0401</t>
+  </si>
+  <si>
+    <t>0.0398,0.0842,0.9206,0.0159</t>
+  </si>
+  <si>
+    <t>0.1287,0.0202,0.7395,0.1588</t>
+  </si>
+  <si>
+    <t>0.0032,0.1528,0.9818,0.0017</t>
+  </si>
+  <si>
+    <t>0.0089,0.9413,0.0608,0.0017</t>
+  </si>
+  <si>
+    <t>0.0094,0.0562,0.9415,0.0126</t>
+  </si>
+  <si>
+    <t>0.0573,0.6885,0.0206,0.4951</t>
+  </si>
+  <si>
+    <t>0.0161,0.9501,0.0221,0.0159</t>
+  </si>
+  <si>
+    <t>0.0023,0.9746,0.2390,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.9821,0.0347,0.0029</t>
+  </si>
+  <si>
+    <t>0.0010,0.3773,0.9779,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.1483,0.9941,0.0008</t>
+  </si>
+  <si>
+    <t>0.0264,0.0090,0.9208,0.0750</t>
+  </si>
+  <si>
+    <t>0.0150,0.0037,0.9792,0.0034</t>
+  </si>
+  <si>
+    <t>0.0164,0.4031,0.7475,0.0204</t>
+  </si>
+  <si>
+    <t>0.0179,0.1054,0.9427,0.0018</t>
+  </si>
+  <si>
+    <t>0.8662,0.1927,0.0136,0.0024</t>
+  </si>
+  <si>
+    <t>0.9637,0.0126,0.0124,0.0058</t>
+  </si>
+  <si>
+    <t>0.9927,0.0030,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.0125,0.9907,0.0068</t>
+  </si>
+  <si>
+    <t>0.9811,0.0136,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.9934,0.0027,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9926,0.0063,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.6420,0.9284,0.0010</t>
+  </si>
+  <si>
+    <t>0.0205,0.0504,0.9373,0.0150</t>
+  </si>
+  <si>
+    <t>0.0027,0.0447,0.9594,0.0194</t>
+  </si>
+  <si>
+    <t>0.0004,0.9626,0.9242,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0181,0.9903,0.0040</t>
+  </si>
+  <si>
+    <t>0.0242,0.8641,0.2248,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9927,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.8438,0.0175,0.1604,0.0114</t>
+  </si>
+  <si>
+    <t>0.3788,0.6100,0.0768,0.0057</t>
+  </si>
+  <si>
+    <t>0.0013,0.0787,0.9441,0.0119</t>
+  </si>
+  <si>
+    <t>0.0011,0.8616,0.9449,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9357,0.9602,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9830,0.6665,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9721,0.6569,0.0002</t>
+  </si>
+  <si>
+    <t>0.0261,0.0019,0.0091,0.9835</t>
+  </si>
+  <si>
+    <t>0.0014,0.0618,0.0002,0.9967</t>
+  </si>
+  <si>
+    <t>0.0061,0.0226,0.0002,0.9953</t>
+  </si>
+  <si>
+    <t>0.0087,0.0030,0.0065,0.9922</t>
+  </si>
+  <si>
+    <t>0.0087,0.0012,0.0066,0.9929</t>
+  </si>
+  <si>
+    <t>0.0015,0.0095,0.0004,0.9983</t>
+  </si>
+  <si>
+    <t>0.0001,0.9904,0.7974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.8646,0.9731,0.0001</t>
+  </si>
+  <si>
+    <t>0.0125,0.6224,0.8906,0.0042</t>
+  </si>
+  <si>
+    <t>0.0022,0.6485,0.9569,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.9175,0.9221,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.8126,0.9559,0.0003</t>
+  </si>
+  <si>
+    <t>0.9758,0.0231,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.9358,0.1029,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9818,0.0346,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9880,0.0113,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9533,0.0687,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9664,0.0399,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.9843,0.0168,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0044,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9956,0.0026,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9821,0.0165,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0152,0.0120,0.8987,0.1692</t>
+  </si>
+  <si>
+    <t>0.1028,0.0346,0.9150,0.0007</t>
+  </si>
+  <si>
+    <t>0.7417,0.0103,0.2931,0.0099</t>
+  </si>
+  <si>
+    <t>0.2558,0.0028,0.8247,0.0047</t>
+  </si>
+  <si>
+    <t>0.0034,0.9916,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0188,0.9772,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0548,0.9435,0.0052,0.0024</t>
+  </si>
+  <si>
+    <t>0.1772,0.9132,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.0117,0.9788,0.0294,0.0004</t>
+  </si>
+  <si>
+    <t>0.0095,0.9870,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.2153,0.8477,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.5861,0.3913,0.0787,0.0167</t>
+  </si>
+  <si>
+    <t>0.0536,0.0164,0.9365,0.0065</t>
+  </si>
+  <si>
+    <t>0.6159,0.2005,0.1754,0.0754</t>
+  </si>
+  <si>
+    <t>0.2260,0.1114,0.7002,0.0071</t>
+  </si>
+  <si>
+    <t>0.1168,0.0882,0.0748,0.8867</t>
+  </si>
+  <si>
+    <t>0.0167,0.9787,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.0094,0.9737,0.0583,0.0004</t>
+  </si>
+  <si>
+    <t>0.0158,0.7579,0.0272,0.5730</t>
+  </si>
+  <si>
+    <t>0.0020,0.8528,0.9097,0.0005</t>
+  </si>
+  <si>
+    <t>0.0083,0.9863,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.8755,0.1589,0.0183,0.0028</t>
+  </si>
+  <si>
+    <t>0.1598,0.8617,0.0190,0.0007</t>
+  </si>
+  <si>
+    <t>0.9496,0.0306,0.0045,0.0101</t>
+  </si>
+  <si>
+    <t>0.9829,0.0133,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9790,0.0218,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9840,0.0024,0.0013,0.0056</t>
+  </si>
+  <si>
+    <t>0.9854,0.0047,0.0008,0.0035</t>
+  </si>
+  <si>
+    <t>0.9191,0.0664,0.0290,0.0022</t>
+  </si>
+  <si>
+    <t>0.9870,0.0055,0.0010,0.0023</t>
+  </si>
+  <si>
+    <t>0.9887,0.0027,0.0004,0.0036</t>
+  </si>
+  <si>
+    <t>0.0019,0.8561,0.9483,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.8299,0.9547,0.0000</t>
+  </si>
+  <si>
+    <t>0.0082,0.7511,0.9142,0.0022</t>
+  </si>
+  <si>
+    <t>0.0100,0.2110,0.9521,0.0007</t>
+  </si>
+  <si>
+    <t>0.7602,0.0556,0.1487,0.0180</t>
+  </si>
+  <si>
+    <t>0.6166,0.0769,0.3961,0.0103</t>
+  </si>
+  <si>
+    <t>0.5060,0.0055,0.6254,0.0091</t>
+  </si>
+  <si>
+    <t>0.5712,0.1375,0.3358,0.0143</t>
+  </si>
+  <si>
+    <t>0.1329,0.0007,0.0007,0.9627</t>
+  </si>
+  <si>
+    <t>0.0011,0.0032,0.0008,0.9989</t>
+  </si>
+  <si>
+    <t>0.0014,0.0264,0.0008,0.9973</t>
+  </si>
+  <si>
+    <t>0.0111,0.0008,0.0106,0.9898</t>
+  </si>
+  <si>
+    <t>0.0020,0.8484,0.7025,0.0065</t>
+  </si>
+  <si>
+    <t>0.9856,0.0078,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.8410,0.2606,0.0069,0.0014</t>
+  </si>
+  <si>
+    <t>0.9611,0.0337,0.0045,0.0021</t>
+  </si>
+  <si>
+    <t>0.4640,0.6642,0.0078,0.0008</t>
+  </si>
+  <si>
+    <t>0.9683,0.0069,0.0051,0.0084</t>
+  </si>
+  <si>
+    <t>0.4337,0.0034,0.0116,0.6484</t>
+  </si>
+  <si>
+    <t>0.9648,0.0045,0.0108,0.0081</t>
+  </si>
+  <si>
+    <t>0.0007,0.0181,0.9888,0.0135</t>
+  </si>
+  <si>
+    <t>0.9742,0.0006,0.0027,0.0139</t>
+  </si>
+  <si>
+    <t>0.9441,0.0035,0.0095,0.0362</t>
+  </si>
+  <si>
+    <t>0.1513,0.8852,0.0114,0.0020</t>
+  </si>
+  <si>
+    <t>0.7259,0.3563,0.0051,0.0058</t>
+  </si>
+  <si>
+    <t>0.9086,0.0429,0.0391,0.0077</t>
+  </si>
+  <si>
+    <t>0.0189,0.9687,0.0018,0.0030</t>
+  </si>
+  <si>
+    <t>0.8010,0.1914,0.0356,0.0053</t>
+  </si>
+  <si>
+    <t>0.6265,0.3161,0.1141,0.0122</t>
+  </si>
+  <si>
+    <t>0.9954,0.0018,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9882,0.0054,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9866,0.0006,0.0001,0.0114</t>
+  </si>
+  <si>
+    <t>0.9927,0.0003,0.0003,0.0042</t>
+  </si>
+  <si>
+    <t>0.9833,0.0073,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9865,0.0137,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9906,0.0014,0.0008,0.0030</t>
+  </si>
+  <si>
+    <t>0.9918,0.0017,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.2995,0.8041,0.0041,0.0035</t>
+  </si>
+  <si>
+    <t>0.5461,0.5292,0.0266,0.0026</t>
+  </si>
+  <si>
+    <t>0.2198,0.8723,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.6663,0.1876,0.2223,0.0161</t>
+  </si>
+  <si>
+    <t>0.9303,0.1472,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.8332,0.1521,0.0434,0.0055</t>
+  </si>
+  <si>
+    <t>0.9229,0.0909,0.0064,0.0037</t>
+  </si>
+  <si>
+    <t>0.5701,0.5406,0.0120,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.1027,0.9885,0.0006</t>
+  </si>
+  <si>
+    <t>0.8652,0.1382,0.0261,0.0048</t>
+  </si>
+  <si>
+    <t>0.0122,0.0084,0.9865,0.0003</t>
+  </si>
+  <si>
+    <t>0.0864,0.0482,0.9179,0.0030</t>
+  </si>
+  <si>
+    <t>0.0112,0.0168,0.9825,0.0011</t>
+  </si>
+  <si>
+    <t>0.0105,0.0444,0.9651,0.0038</t>
+  </si>
+  <si>
+    <t>0.0360,0.0621,0.9394,0.0009</t>
+  </si>
+  <si>
+    <t>0.0625,0.0101,0.9650,0.0001</t>
+  </si>
+  <si>
+    <t>0.0147,0.0189,0.9752,0.0014</t>
+  </si>
+  <si>
+    <t>0.2896,0.0960,0.6844,0.0151</t>
+  </si>
+  <si>
+    <t>0.1972,0.0603,0.7965,0.0058</t>
+  </si>
+  <si>
+    <t>0.2671,0.7280,0.0873,0.0274</t>
+  </si>
+  <si>
+    <t>0.4241,0.1825,0.5126,0.0256</t>
+  </si>
+  <si>
+    <t>0.1545,0.2304,0.7227,0.0062</t>
+  </si>
+  <si>
+    <t>0.3515,0.1286,0.6128,0.0041</t>
+  </si>
+  <si>
+    <t>0.7471,0.0694,0.1990,0.0145</t>
+  </si>
+  <si>
+    <t>0.2086,0.5390,0.3050,0.0048</t>
+  </si>
+  <si>
+    <t>0.4342,0.7273,0.0054,0.0003</t>
+  </si>
+  <si>
+    <t>0.4875,0.7101,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.6872,0.4572,0.0062,0.0010</t>
+  </si>
+  <si>
+    <t>0.9683,0.0421,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.8902,0.1827,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.2790,0.1090,0.6924,0.0095</t>
+  </si>
+  <si>
+    <t>0.8016,0.0137,0.2633,0.0028</t>
+  </si>
+  <si>
+    <t>0.7011,0.0667,0.1122,0.0848</t>
+  </si>
+  <si>
+    <t>0.7216,0.0162,0.3310,0.0099</t>
+  </si>
+  <si>
+    <t>0.8424,0.0412,0.0373,0.0263</t>
+  </si>
+  <si>
+    <t>0.0909,0.0315,0.8999,0.0237</t>
+  </si>
+  <si>
+    <t>0.0137,0.1882,0.9355,0.0081</t>
+  </si>
+  <si>
+    <t>0.0056,0.6586,0.9437,0.0015</t>
+  </si>
+  <si>
+    <t>0.0529,0.1055,0.9223,0.0073</t>
+  </si>
+  <si>
+    <t>0.0035,0.7607,0.8685,0.0033</t>
+  </si>
+  <si>
+    <t>0.9860,0.0053,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.9856,0.0189,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9824,0.0159,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9331,0.1170,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9828,0.0105,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9740,0.0245,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9805,0.0059,0.0006,0.0065</t>
+  </si>
+  <si>
+    <t>0.9858,0.0085,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.0350,0.0128,0.9661,0.0037</t>
+  </si>
+  <si>
+    <t>0.2606,0.2753,0.5850,0.0112</t>
+  </si>
+  <si>
+    <t>0.7983,0.1234,0.0718,0.0096</t>
+  </si>
+  <si>
+    <t>0.0374,0.0082,0.9772,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0978,0.9791,0.0011</t>
+  </si>
+  <si>
+    <t>0.0230,0.1509,0.9112,0.0060</t>
+  </si>
+  <si>
+    <t>0.0033,0.0087,0.9886,0.0027</t>
+  </si>
+  <si>
+    <t>0.0520,0.0157,0.9455,0.0006</t>
+  </si>
+  <si>
+    <t>0.0091,0.0082,0.9872,0.0016</t>
+  </si>
+  <si>
+    <t>0.0066,0.0119,0.9897,0.0005</t>
+  </si>
+  <si>
+    <t>0.5236,0.0613,0.5272,0.0283</t>
+  </si>
+  <si>
+    <t>0.5315,0.0831,0.4607,0.0417</t>
+  </si>
+  <si>
+    <t>0.6477,0.0096,0.4677,0.0058</t>
+  </si>
+  <si>
+    <t>0.6032,0.2497,0.0944,0.0684</t>
+  </si>
+  <si>
+    <t>0.9904,0.0048,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9752,0.0288,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.9911,0.0086,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9738,0.0332,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0043,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9912,0.0106,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9687,0.0372,0.0022,0.0015</t>
+  </si>
+  <si>
+    <t>0.9730,0.0322,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.0129,0.1241,0.9080,0.0018</t>
+  </si>
+  <si>
+    <t>0.0014,0.1039,0.9903,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.0294,0.9760,0.0043</t>
+  </si>
+  <si>
+    <t>0.0421,0.0099,0.9491,0.0039</t>
+  </si>
+  <si>
+    <t>0.0021,0.0150,0.9882,0.0032</t>
+  </si>
+  <si>
+    <t>0.2795,0.0471,0.5662,0.1818</t>
+  </si>
+  <si>
+    <t>0.2335,0.0058,0.8493,0.0022</t>
+  </si>
+  <si>
+    <t>0.0499,0.0387,0.9028,0.0238</t>
+  </si>
+  <si>
+    <t>0.8914,0.0289,0.0181,0.0245</t>
+  </si>
+  <si>
+    <t>0.0044,0.0766,0.0002,0.9925</t>
+  </si>
+  <si>
+    <t>0.0401,0.0039,0.0005,0.9868</t>
+  </si>
+  <si>
+    <t>0.0072,0.0046,0.0012,0.9955</t>
+  </si>
+  <si>
+    <t>0.0032,0.0008,0.0012,0.9977</t>
+  </si>
+  <si>
+    <t>0.7113,0.0925,0.0618,0.1361</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2284,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2480,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2990,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,10 +3421,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,10 +4457,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,10 +4877,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
